--- a/data/SI/SI_LCIs_review.xlsx
+++ b/data/SI/SI_LCIs_review.xlsx
@@ -8,35 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/SI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1536" documentId="11_AD4D9D64A577C15A4A5418A680D85C6E5BDEDD8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AFD481F-1317-4526-BF79-CA9493F32072}"/>
+  <xr:revisionPtr revIDLastSave="1655" documentId="11_AD4D9D64A577C15A4A5418A680D85C6E5BDEDD8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4375227A-642B-4B22-8F9D-B9E90364BA2E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
-    <sheet name="Sources" sheetId="1" r:id="rId2"/>
+    <sheet name="LCI_sources" sheetId="1" r:id="rId2"/>
     <sheet name="Param" sheetId="20" r:id="rId3"/>
-    <sheet name="REF" sheetId="17" r:id="rId4"/>
-    <sheet name="lca_alg" sheetId="8" state="hidden" r:id="rId5"/>
-    <sheet name="Material_MetalliCan" sheetId="18" state="hidden" r:id="rId6"/>
+    <sheet name="lca_alg" sheetId="8" state="hidden" r:id="rId4"/>
+    <sheet name="Material_MetalliCan" sheetId="18" state="hidden" r:id="rId5"/>
+    <sheet name="Mat_inference" sheetId="26" r:id="rId6"/>
     <sheet name="Material_Par" sheetId="19" r:id="rId7"/>
-    <sheet name="EI" sheetId="12" r:id="rId8"/>
+    <sheet name="EI_LCIs" sheetId="12" r:id="rId8"/>
     <sheet name="DATA" sheetId="15" r:id="rId9"/>
     <sheet name="PROCESS" sheetId="24" state="hidden" r:id="rId10"/>
     <sheet name="Archetypes" sheetId="21" r:id="rId11"/>
     <sheet name="Flowsheet" sheetId="25" r:id="rId12"/>
     <sheet name="Mat_arch" sheetId="23" r:id="rId13"/>
-    <sheet name="Mat_examples" sheetId="22" r:id="rId14"/>
+    <sheet name="Mat_examples" sheetId="22" state="hidden" r:id="rId14"/>
+    <sheet name="REF" sheetId="17" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">DATA!$A$1:$O$216</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">EI!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">lca_alg!$A$1:$N$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Material_MetalliCan!$A$1:$Q$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">EI_LCIs!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">lca_alg!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">LCI_sources!$A$1:$M$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Mat_inference!$A$1:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Material_MetalliCan!$A$1:$Q$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Material_Par!$B$1:$I$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Param!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">REF!$A$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sources!$A$1:$M$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">REF!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6820" uniqueCount="1612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6992" uniqueCount="1679">
   <si>
     <t>IMPORTED_FROM</t>
   </si>
@@ -4883,118 +4885,319 @@
     <t>Katta2020</t>
   </si>
   <si>
-    <t>Process/Stage</t>
-  </si>
-  <si>
     <t>Material</t>
   </si>
   <si>
-    <t>Typical Range or Formula</t>
-  </si>
-  <si>
     <t>Drilling &amp; Blasting</t>
   </si>
   <si>
-    <t>Explosives (ANFO)</t>
-  </si>
-  <si>
-    <t>kg/tonne ore</t>
-  </si>
-  <si>
-    <t>0.3â€“0.6</t>
-  </si>
-  <si>
-    <t>SME Handbook; NI 43-101 (Free-milling Au)</t>
-  </si>
-  <si>
-    <t>Comminution (Grinding)</t>
-  </si>
-  <si>
-    <t>Grinding Media (Steel)</t>
-  </si>
-  <si>
-    <t>0.5â€“2.0</t>
-  </si>
-  <si>
-    <t>Norgate &amp; Haque (2010); plant data</t>
-  </si>
-  <si>
-    <t>g/tonne ore</t>
-  </si>
-  <si>
-    <t>50â€“200</t>
-  </si>
-  <si>
-    <t>LCI estimates; mill maintenance logs</t>
-  </si>
-  <si>
     <t>Leaching (CIP/CIL)</t>
   </si>
   <si>
-    <t>Sodium Cyanide</t>
-  </si>
-  <si>
-    <t>1.0â€“1.5</t>
-  </si>
-  <si>
-    <t>Norgate &amp; Haque; Goldcorp NI 43-101</t>
-  </si>
-  <si>
-    <t>Lime (pH modifier)</t>
-  </si>
-  <si>
-    <t>Norgate &amp; Haque; operational data</t>
-  </si>
-  <si>
-    <t>Activated Carbon</t>
-  </si>
-  <si>
-    <t>15â€“50</t>
-  </si>
-  <si>
-    <t>Norgate &amp; Haque; adsorption plant data</t>
-  </si>
-  <si>
-    <t>Water/Tailings Treatment</t>
-  </si>
-  <si>
-    <t>10â€“50</t>
-  </si>
-  <si>
-    <t>Water treatment guidelines</t>
-  </si>
-  <si>
-    <t>Backfill (if underground)</t>
-  </si>
-  <si>
-    <t>30â€“100</t>
-  </si>
-  <si>
-    <t>Paste fill literature; De Souza (2003)</t>
-  </si>
-  <si>
-    <t>Heap or Tank Leach (Refractory or Oxidized)</t>
-  </si>
-  <si>
-    <t>Sulfuric Acid</t>
-  </si>
-  <si>
-    <t>0.5â€“3.0</t>
-  </si>
-  <si>
-    <t>Norgate &amp; Haque; if oxide gold or preg-robbing</t>
-  </si>
-  <si>
-    <t>Process Water Circuit</t>
-  </si>
-  <si>
-    <t>Antiscalant</t>
-  </si>
-  <si>
-    <t>5â€“20</t>
-  </si>
-  <si>
-    <t>Process chemical supplier datasheets</t>
+    <t>material_name</t>
+  </si>
+  <si>
+    <t>value_formula</t>
+  </si>
+  <si>
+    <t>reference_flow</t>
+  </si>
+  <si>
+    <t>Frother</t>
+  </si>
+  <si>
+    <t>material_category</t>
+  </si>
+  <si>
+    <t>metals (scrap input)</t>
+  </si>
+  <si>
+    <t>flocculant / coagulant</t>
+  </si>
+  <si>
+    <t>flux / minor reagent</t>
+  </si>
+  <si>
+    <t>reagent / neutralizing gas</t>
+  </si>
+  <si>
+    <t>flocculant / viscosity modifier</t>
+  </si>
+  <si>
+    <t>cement (backfill / binder)</t>
+  </si>
+  <si>
+    <t>unspecified chemical (general)</t>
+  </si>
+  <si>
+    <t>metals (alloying or process input)</t>
+  </si>
+  <si>
+    <t>reagent (flotation activator)</t>
+  </si>
+  <si>
+    <t>fuel (combustion)</t>
+  </si>
+  <si>
+    <t>energy input</t>
+  </si>
+  <si>
+    <t>frother / surfactant</t>
+  </si>
+  <si>
+    <t>thermal energy</t>
+  </si>
+  <si>
+    <t>oxidant</t>
+  </si>
+  <si>
+    <t>reagent (precipitant)</t>
+  </si>
+  <si>
+    <t>pH modifier (alkaline)</t>
+  </si>
+  <si>
+    <t>unclassified</t>
+  </si>
+  <si>
+    <t>flocculant</t>
+  </si>
+  <si>
+    <t>antiscalant</t>
+  </si>
+  <si>
+    <t>gangue / flux</t>
+  </si>
+  <si>
+    <t>surfactant / frother</t>
+  </si>
+  <si>
+    <t>oxidant / leaching agent</t>
+  </si>
+  <si>
+    <t>dispersant / binder</t>
+  </si>
+  <si>
+    <t>metals (structural)</t>
+  </si>
+  <si>
+    <t>metals (reagent / concentrate)</t>
+  </si>
+  <si>
+    <t>reagent / micronutrient</t>
+  </si>
+  <si>
+    <t>reagent / antifreeze</t>
+  </si>
+  <si>
+    <t>flux / gangue</t>
+  </si>
+  <si>
+    <t>reagent / precipitant</t>
+  </si>
+  <si>
+    <t>collector / flotation reagent</t>
+  </si>
+  <si>
+    <t>metals (feedstock)</t>
+  </si>
+  <si>
+    <t>process</t>
+  </si>
+  <si>
+    <t>gold ore processed</t>
+  </si>
+  <si>
+    <t>Typical NaCN dosage for free-milling gold leaching</t>
+  </si>
+  <si>
+    <t>Norgate &amp; Haque (2010); Goldcorp NI 43-101</t>
+  </si>
+  <si>
+    <t>Used to maintain alkaline pH during cyanidation</t>
+  </si>
+  <si>
+    <t>Operational data; Norgate &amp; Haque</t>
+  </si>
+  <si>
+    <t>Flotation</t>
+  </si>
+  <si>
+    <t>Collectors (xanthates)</t>
+  </si>
+  <si>
+    <t>copper ore processed</t>
+  </si>
+  <si>
+    <t>Sulphide collectors used in Cu flotation</t>
+  </si>
+  <si>
+    <t>UNEP (1991); Rio Tinto process guidelines</t>
+  </si>
+  <si>
+    <t>Grinding</t>
+  </si>
+  <si>
+    <t>Wear rate depends on ore abrasiveness</t>
+  </si>
+  <si>
+    <t>Norgate &amp; Haque (2010); plant benchmarks</t>
+  </si>
+  <si>
+    <t>Direct Shipping Ore</t>
+  </si>
+  <si>
+    <t>iron ore mined</t>
+  </si>
+  <si>
+    <t>Blasting required for excavation</t>
+  </si>
+  <si>
+    <t>Iron ore mining technical reports</t>
+  </si>
+  <si>
+    <t>magnetite feed processed</t>
+  </si>
+  <si>
+    <t>Leaching</t>
+  </si>
+  <si>
+    <t>uranium ore processed</t>
+  </si>
+  <si>
+    <t>Leaching reagent; varies with carbonate content</t>
+  </si>
+  <si>
+    <t>High-grade polymetallic Pb-Zn-Ag</t>
+  </si>
+  <si>
+    <t>Pb-Zn ore processed</t>
+  </si>
+  <si>
+    <t>pH control for differential flotation</t>
+  </si>
+  <si>
+    <t>Polymetallic flotation practice (NI 43-101s)</t>
+  </si>
+  <si>
+    <t>Adsorption &amp; Recovery</t>
+  </si>
+  <si>
+    <t>Used in CIP/CIL circuits to adsorb gold from solution</t>
+  </si>
+  <si>
+    <t>Norgate &amp; Haque; gold plant data</t>
+  </si>
+  <si>
+    <t>Water treatment / Tailings</t>
+  </si>
+  <si>
+    <t>Polyacrylamide-based flocculants for tailings thickening</t>
+  </si>
+  <si>
+    <t>Gold mill operations; supplier data</t>
+  </si>
+  <si>
+    <t>Frother (MIBC or Dowfroth)</t>
+  </si>
+  <si>
+    <t>Frother dosage depends on cell type and mineralogy</t>
+  </si>
+  <si>
+    <t>Flotation reagent guidelines; plant data</t>
+  </si>
+  <si>
+    <t>pH Control</t>
+  </si>
+  <si>
+    <t>Used to depress pyrite and control flotation pH</t>
+  </si>
+  <si>
+    <t>Rio Tinto Cu flotation guide</t>
+  </si>
+  <si>
+    <t>Oxidant to enable uranium solubilization in acid</t>
+  </si>
+  <si>
+    <t>Neutralization</t>
+  </si>
+  <si>
+    <t>Lime or MgO</t>
+  </si>
+  <si>
+    <t>Used to neutralize acid tailings and precipitate metals</t>
+  </si>
+  <si>
+    <t>Depends on ore hardness and liberation grind</t>
+  </si>
+  <si>
+    <t>Magnetite concentrator benchmarks</t>
+  </si>
+  <si>
+    <t>Collectors (e.g., dithiophosphate)</t>
+  </si>
+  <si>
+    <t>Differential flotation of galena/sphalerite</t>
+  </si>
+  <si>
+    <t>Pb-Zn flotation best practices</t>
+  </si>
+  <si>
+    <t>To stabilize froth for selective recovery</t>
+  </si>
+  <si>
+    <t>Mineral processing design texts</t>
+  </si>
+  <si>
+    <t>Parker et al (2016)</t>
+  </si>
+  <si>
+    <t>0.1-0.3 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>1.0-1.5 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>0.5-2.0 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>15-50 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>18537 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>1.0-3.0 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>0.05-0.1 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>0.01-0.03 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>20-50 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>45749 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>43952 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>0.3-1.0 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>0.5-1.0 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>1.5-3.0 * ore_processed_t</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-grade U acid-leach mills </t>
   </si>
 </sst>
 </file>
@@ -5006,7 +5209,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="175" formatCode="0.0000000000"/>
+    <numFmt numFmtId="168" formatCode="0.0000000000"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -5166,7 +5369,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5265,8 +5468,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="175" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -9736,6 +9940,63 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9A03EB-833B-4B1B-B0BB-3F458119FC69}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="B2" s="36" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="B3" s="36" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="36"/>
+      <c r="B4" s="36" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="36"/>
+      <c r="B5" s="36" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="36"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="36"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B1" xr:uid="{AE9A03EB-833B-4B1B-B0BB-3F458119FC69}"/>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://publications.anl.gov/anlpubs/2022/12/178670.pdf" xr:uid="{981A3FDC-B0B2-4E32-AE0A-7437A7273104}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://doi.org/10.1016/j.jclepro.2012.01.042" xr:uid="{15A16E0D-D4BD-4E77-94D2-D8B83559665B}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://doi.org/10.1016/j.jclepro.2012.09.027" xr:uid="{698FA6B7-EB50-44BE-A24B-029699CB864E}"/>
+    <hyperlink ref="B5" r:id="rId4" display="https://doi.org/10.1007/s11367-021-02018-5" xr:uid="{FFF38CF5-FD76-45D9-B517-AC34CE0A5D21}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
@@ -13224,63 +13485,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9A03EB-833B-4B1B-B0BB-3F458119FC69}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.6328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="B2" s="36" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="B3" s="36" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="36"/>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="36"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B1" xr:uid="{AE9A03EB-833B-4B1B-B0BB-3F458119FC69}"/>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://publications.anl.gov/anlpubs/2022/12/178670.pdf" xr:uid="{981A3FDC-B0B2-4E32-AE0A-7437A7273104}"/>
-    <hyperlink ref="B3" r:id="rId2" display="https://doi.org/10.1016/j.jclepro.2012.01.042" xr:uid="{15A16E0D-D4BD-4E77-94D2-D8B83559665B}"/>
-    <hyperlink ref="B4" r:id="rId3" display="https://doi.org/10.1016/j.jclepro.2012.09.027" xr:uid="{698FA6B7-EB50-44BE-A24B-029699CB864E}"/>
-    <hyperlink ref="B5" r:id="rId4" display="https://doi.org/10.1007/s11367-021-02018-5" xr:uid="{FFF38CF5-FD76-45D9-B517-AC34CE0A5D21}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64BEB87F-BEE5-4758-9795-D4CDA3863B29}">
   <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="14.5"/>
@@ -14157,7 +14361,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3333FA4-71D9-42BC-8BAF-D6CA94901908}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:M60"/>
@@ -16658,13 +16862,532 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10DB2E38-2A4D-4F72-9097-A7251786B789}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="48.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D1" t="s">
+        <v>840</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F1" t="s">
+        <v>510</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="H1" t="s">
+        <v>514</v>
+      </c>
+      <c r="I1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E2" s="48" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F2" t="s">
+        <v>362</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1629</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>982</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C3" t="s">
+        <v>917</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E3" s="48" t="s">
+        <v>1664</v>
+      </c>
+      <c r="F3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1614</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>982</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C4" t="s">
+        <v>370</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E4" s="48" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F4" t="s">
+        <v>362</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1614</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1617</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>982</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C5" t="s">
+        <v>941</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E5" s="48" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1677</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1614</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1640</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>982</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C6" t="s">
+        <v>848</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>1667</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1677</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1614</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1643</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C7" t="s">
+        <v>370</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F7" t="s">
+        <v>362</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1636</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1637</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F8" t="s">
+        <v>362</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1636</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1658</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F9" t="s">
+        <v>362</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1636</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1660</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C10" t="s">
+        <v>369</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>1671</v>
+      </c>
+      <c r="F10" t="s">
+        <v>362</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1633</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1634</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F11" t="s">
+        <v>362</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1633</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1651</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F12" t="s">
+        <v>362</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1633</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1654</v>
+      </c>
+      <c r="I12" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C13" t="s">
+        <v>863</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E13" s="48" t="s">
+        <v>1674</v>
+      </c>
+      <c r="F13" t="s">
+        <v>362</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1631</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1655</v>
+      </c>
+      <c r="I13" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F14" t="s">
+        <v>362</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1621</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1622</v>
+      </c>
+      <c r="I14" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C15" t="s">
+        <v>863</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E15" s="48" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F15" t="s">
+        <v>362</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1621</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1625</v>
+      </c>
+      <c r="I15" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E16" s="48" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F16" t="s">
+        <v>362</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1621</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1646</v>
+      </c>
+      <c r="I16" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C17" t="s">
+        <v>370</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E17" s="48" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F17" t="s">
+        <v>362</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1621</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1649</v>
+      </c>
+      <c r="I17" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I17" xr:uid="{10DB2E38-2A4D-4F72-9097-A7251786B789}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I17">
+      <sortCondition ref="A1:A17"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9789708F-4D14-47E8-8972-C29E88103FB2}">
   <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.08984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.7265625" bestFit="1" customWidth="1"/>
@@ -18170,225 +18893,35 @@
         <v>996</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
-      <c r="A44" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B44" t="s">
-        <v>1574</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1575</v>
-      </c>
-      <c r="D44" t="s">
-        <v>324</v>
-      </c>
-      <c r="E44" t="s">
-        <v>1576</v>
-      </c>
-      <c r="F44" t="s">
-        <v>449</v>
-      </c>
-    </row>
     <row r="45" spans="1:12">
-      <c r="A45" t="s">
-        <v>982</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1577</v>
-      </c>
-      <c r="C45" t="s">
-        <v>1578</v>
-      </c>
-      <c r="D45" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E45" t="s">
-        <v>1580</v>
-      </c>
-      <c r="F45" t="s">
-        <v>1581</v>
-      </c>
+      <c r="E45" s="48"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" t="s">
-        <v>982</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1582</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1583</v>
-      </c>
-      <c r="D46" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E46" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F46" t="s">
-        <v>1585</v>
-      </c>
+      <c r="E46" s="48"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" t="s">
-        <v>982</v>
-      </c>
-      <c r="B47" t="s">
-        <v>1582</v>
-      </c>
-      <c r="C47" t="s">
-        <v>865</v>
-      </c>
-      <c r="D47" t="s">
-        <v>1586</v>
-      </c>
-      <c r="E47" t="s">
-        <v>1587</v>
-      </c>
-      <c r="F47" t="s">
-        <v>1588</v>
-      </c>
+      <c r="E47" s="48"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" t="s">
-        <v>982</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C48" t="s">
-        <v>1590</v>
-      </c>
-      <c r="D48" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E48" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F48" t="s">
-        <v>1592</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" t="s">
-        <v>982</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1593</v>
-      </c>
-      <c r="D49" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E49" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F49" t="s">
-        <v>1594</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" t="s">
-        <v>982</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1595</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1586</v>
-      </c>
-      <c r="E50" t="s">
-        <v>1596</v>
-      </c>
-      <c r="F50" t="s">
-        <v>1597</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" t="s">
-        <v>982</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1598</v>
-      </c>
-      <c r="C51" t="s">
-        <v>848</v>
-      </c>
-      <c r="D51" t="s">
-        <v>1586</v>
-      </c>
-      <c r="E51" t="s">
-        <v>1599</v>
-      </c>
-      <c r="F51" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" t="s">
-        <v>982</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1601</v>
-      </c>
-      <c r="C52" t="s">
-        <v>861</v>
-      </c>
-      <c r="D52" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E52" t="s">
-        <v>1602</v>
-      </c>
-      <c r="F52" t="s">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" t="s">
-        <v>982</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1604</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1605</v>
-      </c>
-      <c r="D53" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E53" t="s">
-        <v>1606</v>
-      </c>
-      <c r="F53" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" t="s">
-        <v>982</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1609</v>
-      </c>
-      <c r="D54" t="s">
-        <v>1586</v>
-      </c>
-      <c r="E54" t="s">
-        <v>1610</v>
-      </c>
-      <c r="F54" t="s">
-        <v>1611</v>
-      </c>
+      <c r="E48" s="48"/>
+    </row>
+    <row r="49" spans="5:5">
+      <c r="E49" s="48"/>
+    </row>
+    <row r="50" spans="5:5">
+      <c r="E50" s="48"/>
+    </row>
+    <row r="51" spans="5:5">
+      <c r="E51" s="48"/>
+    </row>
+    <row r="52" spans="5:5">
+      <c r="E52" s="48"/>
+    </row>
+    <row r="53" spans="5:5">
+      <c r="E53" s="48"/>
+    </row>
+    <row r="54" spans="5:5">
+      <c r="E54" s="48"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:I38" xr:uid="{9789708F-4D14-47E8-8972-C29E88103FB2}"/>
@@ -18398,7 +18931,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FACF74F-491F-4A30-A5B5-5AB6F49A038D}">
-  <dimension ref="A1:K137"/>
+  <dimension ref="A1:L137"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="37.453125" bestFit="1" customWidth="1"/>
@@ -18412,9 +18945,10 @@
     <col min="9" max="9" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="255.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>570</v>
       </c>
@@ -18448,8 +18982,11 @@
       <c r="K1" s="1" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="1" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>704</v>
       </c>
@@ -18483,8 +19020,11 @@
       <c r="K2" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>704</v>
       </c>
@@ -18518,8 +19058,11 @@
       <c r="K3" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>704</v>
       </c>
@@ -18553,8 +19096,11 @@
       <c r="K4" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>704</v>
       </c>
@@ -18588,8 +19134,11 @@
       <c r="K5" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>704</v>
       </c>
@@ -18623,8 +19172,11 @@
       <c r="K6" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>704</v>
       </c>
@@ -18658,8 +19210,11 @@
       <c r="K7" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>704</v>
       </c>
@@ -18693,8 +19248,11 @@
       <c r="K8" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>704</v>
       </c>
@@ -18728,8 +19286,11 @@
       <c r="K9" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>704</v>
       </c>
@@ -18763,8 +19324,11 @@
       <c r="K10" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>704</v>
       </c>
@@ -18798,8 +19362,11 @@
       <c r="K11" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>704</v>
       </c>
@@ -18833,8 +19400,11 @@
       <c r="K12" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>704</v>
       </c>
@@ -18868,8 +19438,11 @@
       <c r="K13" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="29">
+      <c r="L13" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="29">
       <c r="A14" t="s">
         <v>704</v>
       </c>
@@ -18903,8 +19476,11 @@
       <c r="K14" s="6" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>704</v>
       </c>
@@ -18938,8 +19514,11 @@
       <c r="K15" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>704</v>
       </c>
@@ -18973,8 +19552,11 @@
       <c r="K16" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="29">
+      <c r="L16" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="29">
       <c r="A17" t="s">
         <v>704</v>
       </c>
@@ -19008,8 +19590,11 @@
       <c r="K17" s="6" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>704</v>
       </c>
@@ -19043,8 +19628,11 @@
       <c r="K18" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>704</v>
       </c>
@@ -19078,8 +19666,11 @@
       <c r="K19" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>704</v>
       </c>
@@ -19113,8 +19704,11 @@
       <c r="K20" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>704</v>
       </c>
@@ -19148,8 +19742,11 @@
       <c r="K21" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>704</v>
       </c>
@@ -19183,8 +19780,11 @@
       <c r="K22" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>704</v>
       </c>
@@ -19218,8 +19818,11 @@
       <c r="K23" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
         <v>704</v>
       </c>
@@ -19253,8 +19856,11 @@
       <c r="K24" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
         <v>704</v>
       </c>
@@ -19288,8 +19894,11 @@
       <c r="K25" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
         <v>704</v>
       </c>
@@ -19323,8 +19932,11 @@
       <c r="K26" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="L26" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
         <v>704</v>
       </c>
@@ -19358,8 +19970,11 @@
       <c r="K27" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="29">
+      <c r="L27" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="29">
       <c r="A28" t="s">
         <v>704</v>
       </c>
@@ -19393,8 +20008,11 @@
       <c r="K28" s="6" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="L28" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
         <v>704</v>
       </c>
@@ -19428,8 +20046,11 @@
       <c r="K29" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="L29" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
         <v>704</v>
       </c>
@@ -19463,8 +20084,11 @@
       <c r="K30" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
         <v>704</v>
       </c>
@@ -19498,8 +20122,11 @@
       <c r="K31" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="L31" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
         <v>704</v>
       </c>
@@ -19533,8 +20160,11 @@
       <c r="K32" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" ht="29">
+      <c r="L32" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="29">
       <c r="A33" t="s">
         <v>704</v>
       </c>
@@ -19568,8 +20198,11 @@
       <c r="K33" s="6" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="L33" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
         <v>704</v>
       </c>
@@ -19603,8 +20236,11 @@
       <c r="K34" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="L34" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
         <v>704</v>
       </c>
@@ -19638,8 +20274,11 @@
       <c r="K35" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="L35" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36" t="s">
         <v>704</v>
       </c>
@@ -19673,8 +20312,11 @@
       <c r="K36" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="L36" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" t="s">
         <v>704</v>
       </c>
@@ -19708,8 +20350,11 @@
       <c r="K37" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="L37" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38" t="s">
         <v>704</v>
       </c>
@@ -19743,8 +20388,11 @@
       <c r="K38" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="L38" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
         <v>704</v>
       </c>
@@ -19778,8 +20426,11 @@
       <c r="K39" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="L39" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" t="s">
         <v>704</v>
       </c>
@@ -19813,8 +20464,11 @@
       <c r="K40" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="L40" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" t="s">
         <v>704</v>
       </c>
@@ -19848,8 +20502,11 @@
       <c r="K41" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="L41" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42" t="s">
         <v>704</v>
       </c>
@@ -19883,8 +20540,11 @@
       <c r="K42" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="43" spans="1:11">
+      <c r="L42" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
         <v>704</v>
       </c>
@@ -19918,8 +20578,11 @@
       <c r="K43" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="L43" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44" t="s">
         <v>704</v>
       </c>
@@ -19953,8 +20616,11 @@
       <c r="K44" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="L44" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45" t="s">
         <v>704</v>
       </c>
@@ -19988,8 +20654,11 @@
       <c r="K45" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="46" spans="1:11">
+      <c r="L45" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46" t="s">
         <v>704</v>
       </c>
@@ -20023,8 +20692,11 @@
       <c r="K46" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" ht="43.5">
+      <c r="L46" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="43.5">
       <c r="A47" t="s">
         <v>269</v>
       </c>
@@ -20058,8 +20730,11 @@
       <c r="K47" s="6" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" ht="29">
+      <c r="L47" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="29">
       <c r="A48" t="s">
         <v>269</v>
       </c>
@@ -20093,8 +20768,11 @@
       <c r="K48" s="6" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="49" spans="1:11">
+      <c r="L48" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
         <v>269</v>
       </c>
@@ -20128,8 +20806,11 @@
       <c r="K49" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" ht="29">
+      <c r="L49" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="29">
       <c r="A50" t="s">
         <v>269</v>
       </c>
@@ -20163,8 +20844,11 @@
       <c r="K50" s="6" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="51" spans="1:11">
+      <c r="L50" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" t="s">
         <v>269</v>
       </c>
@@ -20198,8 +20882,11 @@
       <c r="K51" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="52" spans="1:11">
+      <c r="L51" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" t="s">
         <v>269</v>
       </c>
@@ -20233,8 +20920,11 @@
       <c r="K52" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" ht="29">
+      <c r="L52" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="29">
       <c r="A53" t="s">
         <v>269</v>
       </c>
@@ -20268,8 +20958,11 @@
       <c r="K53" s="6" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" ht="58">
+      <c r="L53" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="58">
       <c r="A54" t="s">
         <v>269</v>
       </c>
@@ -20303,8 +20996,11 @@
       <c r="K54" s="6" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" ht="29">
+      <c r="L54" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="29">
       <c r="A55" t="s">
         <v>269</v>
       </c>
@@ -20338,8 +21034,11 @@
       <c r="K55" s="6" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="56" spans="1:11">
+      <c r="L55" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" t="s">
         <v>269</v>
       </c>
@@ -20373,8 +21072,11 @@
       <c r="K56" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="L56" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" t="s">
         <v>269</v>
       </c>
@@ -20408,8 +21110,11 @@
       <c r="K57" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="58" spans="1:11">
+      <c r="L57" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58" t="s">
         <v>269</v>
       </c>
@@ -20443,8 +21148,11 @@
       <c r="K58" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" ht="29">
+      <c r="L58" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="29">
       <c r="A59" t="s">
         <v>269</v>
       </c>
@@ -20478,8 +21186,11 @@
       <c r="K59" s="6" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" ht="116">
+      <c r="L59" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="116">
       <c r="A60" t="s">
         <v>269</v>
       </c>
@@ -20513,8 +21224,11 @@
       <c r="K60" s="6" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" ht="29">
+      <c r="L60" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="29">
       <c r="A61" t="s">
         <v>269</v>
       </c>
@@ -20548,8 +21262,11 @@
       <c r="K61" s="6" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" ht="43.5">
+      <c r="L61" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="43.5">
       <c r="A62" t="s">
         <v>269</v>
       </c>
@@ -20583,8 +21300,11 @@
       <c r="K62" s="6" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="63" spans="1:11">
+      <c r="L62" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63" t="s">
         <v>835</v>
       </c>
@@ -20615,8 +21335,11 @@
       <c r="J63" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="64" spans="1:11">
+      <c r="L63" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64" t="s">
         <v>835</v>
       </c>
@@ -20647,8 +21370,11 @@
       <c r="J64" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="65" spans="1:11">
+      <c r="L64" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65" t="s">
         <v>835</v>
       </c>
@@ -20679,8 +21405,11 @@
       <c r="J65" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="66" spans="1:11">
+      <c r="L65" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66" t="s">
         <v>835</v>
       </c>
@@ -20711,8 +21440,11 @@
       <c r="J66" t="s">
         <v>832</v>
       </c>
-    </row>
-    <row r="67" spans="1:11">
+      <c r="L66" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
       <c r="A67" t="s">
         <v>632</v>
       </c>
@@ -20746,8 +21478,11 @@
       <c r="K67" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="68" spans="1:11">
+      <c r="L67" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
       <c r="A68" t="s">
         <v>632</v>
       </c>
@@ -20781,8 +21516,11 @@
       <c r="K68" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" ht="29">
+      <c r="L68" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="29">
       <c r="A69" t="s">
         <v>632</v>
       </c>
@@ -20816,8 +21554,11 @@
       <c r="K69" s="6" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" ht="29">
+      <c r="L69" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="29">
       <c r="A70" t="s">
         <v>632</v>
       </c>
@@ -20851,8 +21592,11 @@
       <c r="K70" s="6" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="71" spans="1:11">
+      <c r="L70" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71" t="s">
         <v>632</v>
       </c>
@@ -20886,8 +21630,11 @@
       <c r="K71" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="72" spans="1:11">
+      <c r="L71" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
       <c r="A72" t="s">
         <v>632</v>
       </c>
@@ -20921,8 +21668,11 @@
       <c r="K72" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="73" spans="1:11">
+      <c r="L72" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
       <c r="A73" t="s">
         <v>632</v>
       </c>
@@ -20956,8 +21706,11 @@
       <c r="K73" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="74" spans="1:11">
+      <c r="L73" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
       <c r="A74" t="s">
         <v>632</v>
       </c>
@@ -20991,8 +21744,11 @@
       <c r="K74" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="75" spans="1:11">
+      <c r="L74" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
       <c r="A75" t="s">
         <v>632</v>
       </c>
@@ -21026,8 +21782,11 @@
       <c r="K75" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="76" spans="1:11">
+      <c r="L75" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
       <c r="A76" t="s">
         <v>632</v>
       </c>
@@ -21061,8 +21820,11 @@
       <c r="K76" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="77" spans="1:11">
+      <c r="L76" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
       <c r="A77" t="s">
         <v>632</v>
       </c>
@@ -21096,8 +21858,11 @@
       <c r="K77" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="78" spans="1:11">
+      <c r="L77" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
       <c r="A78" t="s">
         <v>632</v>
       </c>
@@ -21131,8 +21896,11 @@
       <c r="K78" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="79" spans="1:11">
+      <c r="L78" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
       <c r="A79" t="s">
         <v>295</v>
       </c>
@@ -21166,8 +21934,11 @@
       <c r="K79" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="80" spans="1:11">
+      <c r="L79" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
       <c r="A80" t="s">
         <v>295</v>
       </c>
@@ -21201,8 +21972,11 @@
       <c r="K80" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="81" spans="1:11">
+      <c r="L80" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
       <c r="A81" t="s">
         <v>295</v>
       </c>
@@ -21236,8 +22010,11 @@
       <c r="K81" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="82" spans="1:11">
+      <c r="L81" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82" t="s">
         <v>295</v>
       </c>
@@ -21271,8 +22048,11 @@
       <c r="K82" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="83" spans="1:11">
+      <c r="L82" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
       <c r="A83" t="s">
         <v>295</v>
       </c>
@@ -21306,8 +22086,11 @@
       <c r="K83" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="84" spans="1:11">
+      <c r="L83" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
       <c r="A84" t="s">
         <v>295</v>
       </c>
@@ -21341,8 +22124,11 @@
       <c r="K84" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="85" spans="1:11">
+      <c r="L84" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
       <c r="A85" t="s">
         <v>295</v>
       </c>
@@ -21376,8 +22162,11 @@
       <c r="K85" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="86" spans="1:11">
+      <c r="L85" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
       <c r="A86" t="s">
         <v>295</v>
       </c>
@@ -21412,7 +22201,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:12">
       <c r="A87" t="s">
         <v>295</v>
       </c>
@@ -21447,7 +22236,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:12">
       <c r="A88" t="s">
         <v>295</v>
       </c>
@@ -21482,7 +22271,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:12">
       <c r="A89" t="s">
         <v>295</v>
       </c>
@@ -21517,7 +22306,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:12">
       <c r="A90" t="s">
         <v>295</v>
       </c>
@@ -21552,7 +22341,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:12">
       <c r="A91" t="s">
         <v>295</v>
       </c>
@@ -21587,7 +22376,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:12">
       <c r="A92" t="s">
         <v>295</v>
       </c>
@@ -21622,7 +22411,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:12">
       <c r="A93" t="s">
         <v>295</v>
       </c>
@@ -21657,7 +22446,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:12">
       <c r="A94" t="s">
         <v>295</v>
       </c>
@@ -21692,7 +22481,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:12">
       <c r="A95" t="s">
         <v>295</v>
       </c>
@@ -21727,7 +22516,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:12">
       <c r="A96" t="s">
         <v>295</v>
       </c>
@@ -23090,11 +23879,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{0FACF74F-491F-4A30-A5B5-5AB6F49A038D}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K46">
-      <sortCondition ref="F1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:L1" xr:uid="{0FACF74F-491F-4A30-A5B5-5AB6F49A038D}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -23169,7 +23954,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" hidden="1">
       <c r="A2" t="s">
         <v>897</v>
       </c>
@@ -23213,7 +23998,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" hidden="1">
       <c r="A3" t="s">
         <v>897</v>
       </c>
@@ -23257,7 +24042,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" hidden="1">
       <c r="A4" t="s">
         <v>897</v>
       </c>
@@ -23301,7 +24086,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" hidden="1">
       <c r="A5" t="s">
         <v>897</v>
       </c>
@@ -23345,7 +24130,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" hidden="1">
       <c r="A6" t="s">
         <v>897</v>
       </c>
@@ -23389,7 +24174,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="31" customFormat="1">
+    <row r="7" spans="1:15" s="31" customFormat="1" hidden="1">
       <c r="A7" s="31" t="s">
         <v>897</v>
       </c>
@@ -23433,7 +24218,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="31" customFormat="1">
+    <row r="8" spans="1:15" s="31" customFormat="1" hidden="1">
       <c r="A8" s="31" t="s">
         <v>897</v>
       </c>
@@ -23477,7 +24262,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="31" customFormat="1">
+    <row r="9" spans="1:15" s="31" customFormat="1" hidden="1">
       <c r="A9" s="31" t="s">
         <v>897</v>
       </c>
@@ -23521,7 +24306,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="31" customFormat="1">
+    <row r="10" spans="1:15" s="31" customFormat="1" hidden="1">
       <c r="A10" s="31" t="s">
         <v>897</v>
       </c>
@@ -23565,7 +24350,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="31" customFormat="1">
+    <row r="11" spans="1:15" s="31" customFormat="1" hidden="1">
       <c r="A11" s="31" t="s">
         <v>897</v>
       </c>
@@ -23609,7 +24394,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="31" customFormat="1">
+    <row r="12" spans="1:15" s="31" customFormat="1" hidden="1">
       <c r="A12" s="31" t="s">
         <v>897</v>
       </c>
@@ -23653,7 +24438,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="31" customFormat="1">
+    <row r="13" spans="1:15" s="31" customFormat="1" hidden="1">
       <c r="A13" s="31" t="s">
         <v>897</v>
       </c>
@@ -23697,7 +24482,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="31" customFormat="1">
+    <row r="14" spans="1:15" s="31" customFormat="1" hidden="1">
       <c r="A14" s="31" t="s">
         <v>897</v>
       </c>
@@ -23741,7 +24526,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" hidden="1">
       <c r="A15" t="s">
         <v>897</v>
       </c>
@@ -23785,7 +24570,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" hidden="1">
       <c r="A16" t="s">
         <v>897</v>
       </c>
@@ -23829,7 +24614,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" hidden="1">
       <c r="A17" t="s">
         <v>897</v>
       </c>
@@ -23873,7 +24658,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" hidden="1">
       <c r="A18" t="s">
         <v>897</v>
       </c>
@@ -23917,7 +24702,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" hidden="1">
       <c r="A19" t="s">
         <v>897</v>
       </c>
@@ -23961,7 +24746,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" hidden="1">
       <c r="A20" t="s">
         <v>897</v>
       </c>
@@ -24005,7 +24790,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" hidden="1">
       <c r="A21" t="s">
         <v>897</v>
       </c>
@@ -24049,7 +24834,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" hidden="1">
       <c r="A22" t="s">
         <v>897</v>
       </c>
@@ -24093,7 +24878,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" hidden="1">
       <c r="A23" t="s">
         <v>897</v>
       </c>
@@ -24137,7 +24922,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" hidden="1">
       <c r="A24" t="s">
         <v>897</v>
       </c>
@@ -24181,7 +24966,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" hidden="1">
       <c r="A25" t="s">
         <v>897</v>
       </c>
@@ -24225,7 +25010,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" hidden="1">
       <c r="A26" t="s">
         <v>897</v>
       </c>
@@ -24269,7 +25054,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" hidden="1">
       <c r="A27" t="s">
         <v>897</v>
       </c>
@@ -24313,7 +25098,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" hidden="1">
       <c r="A28" t="s">
         <v>897</v>
       </c>
@@ -24357,7 +25142,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" hidden="1">
       <c r="A29" t="s">
         <v>897</v>
       </c>
@@ -24401,7 +25186,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" hidden="1">
       <c r="A30" t="s">
         <v>897</v>
       </c>
@@ -24445,7 +25230,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" hidden="1">
       <c r="A31" t="s">
         <v>897</v>
       </c>
@@ -24489,7 +25274,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" hidden="1">
       <c r="A32" t="s">
         <v>897</v>
       </c>
@@ -24533,7 +25318,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" hidden="1">
       <c r="A33" t="s">
         <v>897</v>
       </c>
@@ -24577,7 +25362,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="34" spans="1:15" hidden="1">
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
         <v>398</v>
       </c>
@@ -24618,7 +25403,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="35" spans="1:15" hidden="1">
+    <row r="35" spans="1:15">
       <c r="A35" t="s">
         <v>398</v>
       </c>
@@ -24659,7 +25444,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="36" spans="1:15" hidden="1">
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
         <v>398</v>
       </c>
@@ -24700,7 +25485,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="37" spans="1:15" hidden="1">
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
         <v>398</v>
       </c>
@@ -24742,7 +25527,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="38" spans="1:15" hidden="1">
+    <row r="38" spans="1:15">
       <c r="A38" t="s">
         <v>398</v>
       </c>
@@ -24784,7 +25569,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1">
+    <row r="39" spans="1:15">
       <c r="A39" t="s">
         <v>398</v>
       </c>
@@ -24826,7 +25611,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1">
+    <row r="40" spans="1:15">
       <c r="A40" t="s">
         <v>398</v>
       </c>
@@ -24868,7 +25653,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1">
+    <row r="41" spans="1:15">
       <c r="A41" t="s">
         <v>398</v>
       </c>
@@ -24909,7 +25694,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="42" spans="1:15" hidden="1">
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
         <v>398</v>
       </c>
@@ -24950,7 +25735,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="43" spans="1:15" hidden="1">
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
         <v>398</v>
       </c>
@@ -24991,7 +25776,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="44" spans="1:15" hidden="1">
+    <row r="44" spans="1:15">
       <c r="A44" t="s">
         <v>398</v>
       </c>
@@ -25032,7 +25817,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1">
+    <row r="45" spans="1:15">
       <c r="A45" t="s">
         <v>398</v>
       </c>
@@ -25073,7 +25858,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1">
+    <row r="46" spans="1:15">
       <c r="A46" t="s">
         <v>398</v>
       </c>
@@ -25114,7 +25899,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1">
+    <row r="47" spans="1:15">
       <c r="A47" t="s">
         <v>398</v>
       </c>
@@ -25155,7 +25940,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1">
+    <row r="48" spans="1:15">
       <c r="A48" t="s">
         <v>398</v>
       </c>
@@ -25196,7 +25981,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1">
+    <row r="49" spans="1:15">
       <c r="A49" t="s">
         <v>398</v>
       </c>
@@ -25237,7 +26022,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1">
+    <row r="50" spans="1:15">
       <c r="A50" t="s">
         <v>398</v>
       </c>
@@ -25278,7 +26063,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1">
+    <row r="51" spans="1:15">
       <c r="A51" t="s">
         <v>398</v>
       </c>
@@ -25319,7 +26104,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1">
+    <row r="52" spans="1:15">
       <c r="A52" t="s">
         <v>398</v>
       </c>
@@ -25360,7 +26145,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1">
+    <row r="53" spans="1:15">
       <c r="A53" t="s">
         <v>398</v>
       </c>
@@ -25401,7 +26186,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="54" spans="1:15" hidden="1">
+    <row r="54" spans="1:15">
       <c r="A54" t="s">
         <v>398</v>
       </c>
@@ -25442,7 +26227,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1">
+    <row r="55" spans="1:15">
       <c r="A55" t="s">
         <v>398</v>
       </c>
@@ -25483,7 +26268,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="56" spans="1:15" hidden="1">
+    <row r="56" spans="1:15">
       <c r="A56" t="s">
         <v>398</v>
       </c>
@@ -25524,7 +26309,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="57" spans="1:15" hidden="1">
+    <row r="57" spans="1:15">
       <c r="A57" t="s">
         <v>398</v>
       </c>
@@ -25568,7 +26353,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1">
+    <row r="58" spans="1:15">
       <c r="A58" t="s">
         <v>398</v>
       </c>
@@ -25612,7 +26397,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1">
+    <row r="59" spans="1:15">
       <c r="A59" t="s">
         <v>398</v>
       </c>
@@ -25657,7 +26442,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1">
+    <row r="60" spans="1:15">
       <c r="A60" t="s">
         <v>398</v>
       </c>
@@ -25701,7 +26486,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="61" spans="1:15" hidden="1">
+    <row r="61" spans="1:15">
       <c r="A61" t="s">
         <v>398</v>
       </c>
@@ -25745,7 +26530,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="62" spans="1:15" hidden="1">
+    <row r="62" spans="1:15">
       <c r="A62" t="s">
         <v>398</v>
       </c>
@@ -25789,7 +26574,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="63" spans="1:15" hidden="1">
+    <row r="63" spans="1:15">
       <c r="A63" t="s">
         <v>398</v>
       </c>
@@ -25833,7 +26618,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1">
+    <row r="64" spans="1:15">
       <c r="A64" t="s">
         <v>398</v>
       </c>
@@ -25877,7 +26662,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1">
+    <row r="65" spans="1:15">
       <c r="A65" t="s">
         <v>398</v>
       </c>
@@ -25921,7 +26706,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="66" spans="1:15" hidden="1">
+    <row r="66" spans="1:15">
       <c r="A66" t="s">
         <v>398</v>
       </c>
@@ -25965,7 +26750,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="67" spans="1:15" hidden="1">
+    <row r="67" spans="1:15">
       <c r="A67" t="s">
         <v>398</v>
       </c>
@@ -26009,7 +26794,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1">
+    <row r="68" spans="1:15">
       <c r="A68" t="s">
         <v>398</v>
       </c>
@@ -26053,7 +26838,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="69" spans="1:15" hidden="1">
+    <row r="69" spans="1:15">
       <c r="A69" t="s">
         <v>398</v>
       </c>
@@ -26097,7 +26882,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="70" spans="1:15" hidden="1">
+    <row r="70" spans="1:15">
       <c r="A70" t="s">
         <v>398</v>
       </c>
@@ -26141,7 +26926,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="71" spans="1:15" hidden="1">
+    <row r="71" spans="1:15">
       <c r="A71" t="s">
         <v>398</v>
       </c>
@@ -26185,7 +26970,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="72" spans="1:15" hidden="1">
+    <row r="72" spans="1:15">
       <c r="A72" t="s">
         <v>398</v>
       </c>
@@ -26229,7 +27014,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="73" spans="1:15" hidden="1">
+    <row r="73" spans="1:15">
       <c r="A73" t="s">
         <v>398</v>
       </c>
@@ -26273,7 +27058,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="74" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="74" spans="1:15" s="32" customFormat="1">
       <c r="A74" s="32" t="s">
         <v>948</v>
       </c>
@@ -26305,7 +27090,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="75" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="75" spans="1:15" s="32" customFormat="1">
       <c r="A75" s="32" t="s">
         <v>948</v>
       </c>
@@ -26340,7 +27125,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="76" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="76" spans="1:15" s="32" customFormat="1">
       <c r="A76" s="32" t="s">
         <v>948</v>
       </c>
@@ -26375,7 +27160,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="77" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="77" spans="1:15" s="32" customFormat="1">
       <c r="A77" s="32" t="s">
         <v>948</v>
       </c>
@@ -26410,7 +27195,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="78" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="78" spans="1:15" s="32" customFormat="1">
       <c r="A78" s="32" t="s">
         <v>948</v>
       </c>
@@ -26445,7 +27230,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="79" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="79" spans="1:15" s="32" customFormat="1">
       <c r="A79" s="32" t="s">
         <v>948</v>
       </c>
@@ -26480,7 +27265,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="80" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="80" spans="1:15" s="32" customFormat="1">
       <c r="A80" s="32" t="s">
         <v>948</v>
       </c>
@@ -26515,7 +27300,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="81" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="81" spans="1:15" s="32" customFormat="1">
       <c r="A81" s="32" t="s">
         <v>948</v>
       </c>
@@ -26550,7 +27335,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="82" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="82" spans="1:15" s="32" customFormat="1">
       <c r="A82" s="32" t="s">
         <v>948</v>
       </c>
@@ -26585,7 +27370,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="83" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="83" spans="1:15" s="32" customFormat="1">
       <c r="A83" s="32" t="s">
         <v>948</v>
       </c>
@@ -26620,7 +27405,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="84" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="84" spans="1:15" s="32" customFormat="1">
       <c r="A84" s="32" t="s">
         <v>948</v>
       </c>
@@ -26655,7 +27440,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="85" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="85" spans="1:15" s="32" customFormat="1">
       <c r="A85" s="32" t="s">
         <v>948</v>
       </c>
@@ -26690,7 +27475,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="86" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="86" spans="1:15" s="32" customFormat="1">
       <c r="A86" s="32" t="s">
         <v>948</v>
       </c>
@@ -26725,7 +27510,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="87" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="87" spans="1:15" s="32" customFormat="1">
       <c r="A87" s="32" t="s">
         <v>948</v>
       </c>
@@ -26760,7 +27545,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="88" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="88" spans="1:15" s="32" customFormat="1">
       <c r="A88" s="32" t="s">
         <v>948</v>
       </c>
@@ -26795,7 +27580,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="89" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="89" spans="1:15" s="32" customFormat="1">
       <c r="A89" s="32" t="s">
         <v>948</v>
       </c>
@@ -26830,7 +27615,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="90" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="90" spans="1:15" s="32" customFormat="1">
       <c r="A90" s="32" t="s">
         <v>948</v>
       </c>
@@ -26865,7 +27650,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="91" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="91" spans="1:15" s="32" customFormat="1">
       <c r="A91" s="32" t="s">
         <v>948</v>
       </c>
@@ -26900,7 +27685,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="92" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="92" spans="1:15" s="32" customFormat="1">
       <c r="A92" s="32" t="s">
         <v>948</v>
       </c>
@@ -26935,7 +27720,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="93" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="93" spans="1:15" s="32" customFormat="1">
       <c r="A93" s="32" t="s">
         <v>948</v>
       </c>
@@ -26970,7 +27755,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="94" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="94" spans="1:15" s="32" customFormat="1">
       <c r="A94" s="32" t="s">
         <v>948</v>
       </c>
@@ -27005,7 +27790,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="95" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="95" spans="1:15" s="32" customFormat="1">
       <c r="A95" s="32" t="s">
         <v>948</v>
       </c>
@@ -27040,7 +27825,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="96" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="96" spans="1:15" s="32" customFormat="1">
       <c r="A96" s="32" t="s">
         <v>948</v>
       </c>
@@ -27075,7 +27860,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="97" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="97" spans="1:15" s="32" customFormat="1">
       <c r="A97" s="32" t="s">
         <v>948</v>
       </c>
@@ -27110,7 +27895,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="98" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="98" spans="1:15" s="32" customFormat="1">
       <c r="A98" s="32" t="s">
         <v>948</v>
       </c>
@@ -27145,7 +27930,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="99" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="99" spans="1:15" s="32" customFormat="1">
       <c r="A99" s="32" t="s">
         <v>948</v>
       </c>
@@ -27180,7 +27965,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="100" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="100" spans="1:15" s="32" customFormat="1">
       <c r="A100" s="32" t="s">
         <v>948</v>
       </c>
@@ -27215,7 +28000,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="101" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="101" spans="1:15" s="32" customFormat="1">
       <c r="A101" s="32" t="s">
         <v>948</v>
       </c>
@@ -27250,7 +28035,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="102" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="102" spans="1:15" s="32" customFormat="1">
       <c r="A102" s="32" t="s">
         <v>948</v>
       </c>
@@ -27285,7 +28070,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="103" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="103" spans="1:15" s="32" customFormat="1">
       <c r="A103" s="32" t="s">
         <v>948</v>
       </c>
@@ -27320,7 +28105,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="104" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="104" spans="1:15" s="32" customFormat="1">
       <c r="A104" s="32" t="s">
         <v>948</v>
       </c>
@@ -27355,7 +28140,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="105" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="105" spans="1:15" s="32" customFormat="1">
       <c r="A105" s="32" t="s">
         <v>948</v>
       </c>
@@ -27390,7 +28175,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="106" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="106" spans="1:15" s="32" customFormat="1">
       <c r="A106" s="32" t="s">
         <v>948</v>
       </c>
@@ -27425,7 +28210,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="107" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="107" spans="1:15" s="32" customFormat="1">
       <c r="A107" s="32" t="s">
         <v>948</v>
       </c>
@@ -27460,7 +28245,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="108" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="108" spans="1:15" s="32" customFormat="1">
       <c r="A108" s="32" t="s">
         <v>948</v>
       </c>
@@ -27495,7 +28280,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="109" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="109" spans="1:15" s="32" customFormat="1">
       <c r="A109" s="32" t="s">
         <v>948</v>
       </c>
@@ -27530,7 +28315,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="110" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="110" spans="1:15" s="32" customFormat="1">
       <c r="A110" s="32" t="s">
         <v>948</v>
       </c>
@@ -27565,7 +28350,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="111" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="111" spans="1:15" s="32" customFormat="1">
       <c r="A111" s="32" t="s">
         <v>948</v>
       </c>
@@ -27600,7 +28385,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="112" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="112" spans="1:15" s="32" customFormat="1">
       <c r="A112" s="32" t="s">
         <v>948</v>
       </c>
@@ -27635,7 +28420,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="113" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="113" spans="1:15" s="32" customFormat="1">
       <c r="A113" s="32" t="s">
         <v>948</v>
       </c>
@@ -27670,7 +28455,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="114" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="114" spans="1:15" s="32" customFormat="1">
       <c r="A114" s="32" t="s">
         <v>948</v>
       </c>
@@ -27705,7 +28490,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="115" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="115" spans="1:15" s="32" customFormat="1">
       <c r="A115" s="32" t="s">
         <v>948</v>
       </c>
@@ -27740,7 +28525,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="116" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="116" spans="1:15" s="32" customFormat="1">
       <c r="A116" s="32" t="s">
         <v>948</v>
       </c>
@@ -27775,7 +28560,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="117" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="117" spans="1:15" s="32" customFormat="1">
       <c r="A117" s="32" t="s">
         <v>948</v>
       </c>
@@ -27810,7 +28595,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="118" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="118" spans="1:15" s="32" customFormat="1">
       <c r="A118" s="32" t="s">
         <v>948</v>
       </c>
@@ -27845,7 +28630,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="119" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="119" spans="1:15" s="32" customFormat="1">
       <c r="A119" s="32" t="s">
         <v>948</v>
       </c>
@@ -27880,7 +28665,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="120" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="120" spans="1:15" s="32" customFormat="1">
       <c r="A120" s="32" t="s">
         <v>948</v>
       </c>
@@ -27916,7 +28701,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="121" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="121" spans="1:15" s="32" customFormat="1">
       <c r="A121" s="32" t="s">
         <v>948</v>
       </c>
@@ -27952,7 +28737,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="122" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="122" spans="1:15" s="32" customFormat="1">
       <c r="A122" s="32" t="s">
         <v>948</v>
       </c>
@@ -27988,7 +28773,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="123" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="123" spans="1:15" s="32" customFormat="1">
       <c r="A123" s="32" t="s">
         <v>948</v>
       </c>
@@ -28023,7 +28808,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="124" spans="1:15" s="32" customFormat="1" hidden="1">
+    <row r="124" spans="1:15" s="32" customFormat="1">
       <c r="A124" s="32" t="s">
         <v>948</v>
       </c>
@@ -28058,7 +28843,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="125" spans="1:15" hidden="1">
+    <row r="125" spans="1:15">
       <c r="A125" s="34" t="s">
         <v>457</v>
       </c>
@@ -28102,7 +28887,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="126" spans="1:15" hidden="1">
+    <row r="126" spans="1:15">
       <c r="A126" s="34" t="s">
         <v>457</v>
       </c>
@@ -28146,7 +28931,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1">
+    <row r="127" spans="1:15">
       <c r="A127" s="34" t="s">
         <v>457</v>
       </c>
@@ -28190,7 +28975,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="128" spans="1:15" hidden="1">
+    <row r="128" spans="1:15">
       <c r="A128" s="34" t="s">
         <v>457</v>
       </c>
@@ -28234,7 +29019,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1">
+    <row r="129" spans="1:15">
       <c r="A129" s="34" t="s">
         <v>457</v>
       </c>
@@ -28278,7 +29063,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1">
+    <row r="130" spans="1:15">
       <c r="A130" s="34" t="s">
         <v>457</v>
       </c>
@@ -28322,7 +29107,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1">
+    <row r="131" spans="1:15">
       <c r="A131" s="34" t="s">
         <v>457</v>
       </c>
@@ -28366,7 +29151,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1">
+    <row r="132" spans="1:15">
       <c r="A132" s="34" t="s">
         <v>457</v>
       </c>
@@ -28410,7 +29195,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1">
+    <row r="133" spans="1:15">
       <c r="A133" s="34" t="s">
         <v>457</v>
       </c>
@@ -28454,7 +29239,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1">
+    <row r="134" spans="1:15">
       <c r="A134" s="34" t="s">
         <v>457</v>
       </c>
@@ -28498,7 +29283,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1">
+    <row r="135" spans="1:15">
       <c r="A135" s="34" t="s">
         <v>457</v>
       </c>
@@ -28542,7 +29327,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1">
+    <row r="136" spans="1:15">
       <c r="A136" s="34" t="s">
         <v>457</v>
       </c>
@@ -28586,7 +29371,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="137" spans="1:15" hidden="1">
+    <row r="137" spans="1:15">
       <c r="A137" s="34" t="s">
         <v>457</v>
       </c>
@@ -28630,7 +29415,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1">
+    <row r="138" spans="1:15">
       <c r="A138" s="34" t="s">
         <v>457</v>
       </c>
@@ -28674,7 +29459,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1">
+    <row r="139" spans="1:15">
       <c r="A139" s="34" t="s">
         <v>457</v>
       </c>
@@ -28718,7 +29503,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="140" spans="1:15" hidden="1">
+    <row r="140" spans="1:15">
       <c r="A140" s="34" t="s">
         <v>457</v>
       </c>
@@ -28762,7 +29547,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1">
+    <row r="141" spans="1:15">
       <c r="A141" s="34" t="s">
         <v>457</v>
       </c>
@@ -28806,7 +29591,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1">
+    <row r="142" spans="1:15">
       <c r="A142" s="34" t="s">
         <v>457</v>
       </c>
@@ -28850,7 +29635,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1">
+    <row r="143" spans="1:15">
       <c r="A143" s="34" t="s">
         <v>457</v>
       </c>
@@ -28894,7 +29679,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="144" spans="1:15" hidden="1">
+    <row r="144" spans="1:15">
       <c r="A144" s="34" t="s">
         <v>457</v>
       </c>
@@ -28938,7 +29723,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="145" spans="1:15" hidden="1">
+    <row r="145" spans="1:15">
       <c r="A145" s="34" t="s">
         <v>457</v>
       </c>
@@ -28982,7 +29767,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1">
+    <row r="146" spans="1:15">
       <c r="A146" s="34" t="s">
         <v>457</v>
       </c>
@@ -29026,7 +29811,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="147" spans="1:15" hidden="1">
+    <row r="147" spans="1:15">
       <c r="A147" s="34" t="s">
         <v>457</v>
       </c>
@@ -29070,7 +29855,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="148" spans="1:15" hidden="1">
+    <row r="148" spans="1:15">
       <c r="A148" s="34" t="s">
         <v>457</v>
       </c>
@@ -29114,7 +29899,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="149" spans="1:15" hidden="1">
+    <row r="149" spans="1:15">
       <c r="A149" s="34" t="s">
         <v>457</v>
       </c>
@@ -29158,7 +29943,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="150" spans="1:15" hidden="1">
+    <row r="150" spans="1:15">
       <c r="A150" s="34" t="s">
         <v>457</v>
       </c>
@@ -29202,7 +29987,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="151" spans="1:15" hidden="1">
+    <row r="151" spans="1:15">
       <c r="A151" s="34" t="s">
         <v>457</v>
       </c>
@@ -29246,7 +30031,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1">
+    <row r="152" spans="1:15">
       <c r="A152" s="34" t="s">
         <v>457</v>
       </c>
@@ -29290,7 +30075,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1">
+    <row r="153" spans="1:15">
       <c r="A153" s="34" t="s">
         <v>457</v>
       </c>
@@ -29334,7 +30119,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1">
+    <row r="154" spans="1:15">
       <c r="A154" s="34" t="s">
         <v>457</v>
       </c>
@@ -29378,7 +30163,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1">
+    <row r="155" spans="1:15">
       <c r="A155" s="34" t="s">
         <v>457</v>
       </c>
@@ -29422,7 +30207,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1">
+    <row r="156" spans="1:15">
       <c r="A156" s="34" t="s">
         <v>457</v>
       </c>
@@ -29466,7 +30251,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="157" spans="1:15" hidden="1">
+    <row r="157" spans="1:15">
       <c r="A157" s="34" t="s">
         <v>457</v>
       </c>
@@ -29510,7 +30295,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="158" spans="1:15" hidden="1">
+    <row r="158" spans="1:15">
       <c r="A158" s="34" t="s">
         <v>457</v>
       </c>
@@ -29554,7 +30339,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1">
+    <row r="159" spans="1:15">
       <c r="A159" s="34" t="s">
         <v>457</v>
       </c>
@@ -29598,7 +30383,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1">
+    <row r="160" spans="1:15">
       <c r="A160" s="34" t="s">
         <v>457</v>
       </c>
@@ -29642,7 +30427,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1">
+    <row r="161" spans="1:15">
       <c r="A161" s="34" t="s">
         <v>457</v>
       </c>
@@ -29686,7 +30471,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="162" spans="1:15" hidden="1">
+    <row r="162" spans="1:15">
       <c r="A162" s="34" t="s">
         <v>457</v>
       </c>
@@ -29730,7 +30515,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="163" spans="1:15" hidden="1">
+    <row r="163" spans="1:15">
       <c r="A163" s="34" t="s">
         <v>457</v>
       </c>
@@ -29774,7 +30559,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="164" spans="1:15" hidden="1">
+    <row r="164" spans="1:15">
       <c r="A164" s="34" t="s">
         <v>457</v>
       </c>
@@ -29818,7 +30603,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="165" spans="1:15" hidden="1">
+    <row r="165" spans="1:15">
       <c r="A165" s="34" t="s">
         <v>457</v>
       </c>
@@ -29862,7 +30647,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="166" spans="1:15" hidden="1">
+    <row r="166" spans="1:15">
       <c r="A166" s="34" t="s">
         <v>457</v>
       </c>
@@ -29906,7 +30691,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="167" spans="1:15" hidden="1">
+    <row r="167" spans="1:15">
       <c r="A167" s="34" t="s">
         <v>457</v>
       </c>
@@ -29950,7 +30735,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="168" spans="1:15" hidden="1">
+    <row r="168" spans="1:15">
       <c r="A168" s="34" t="s">
         <v>457</v>
       </c>
@@ -29994,7 +30779,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="169" spans="1:15" hidden="1">
+    <row r="169" spans="1:15">
       <c r="A169" s="34" t="s">
         <v>457</v>
       </c>
@@ -30038,7 +30823,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="170" spans="1:15" hidden="1">
+    <row r="170" spans="1:15">
       <c r="A170" s="34" t="s">
         <v>457</v>
       </c>
@@ -30082,7 +30867,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="171" spans="1:15" hidden="1">
+    <row r="171" spans="1:15">
       <c r="A171" s="34" t="s">
         <v>457</v>
       </c>
@@ -30126,7 +30911,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="172" spans="1:15" hidden="1">
+    <row r="172" spans="1:15">
       <c r="A172" s="34" t="s">
         <v>457</v>
       </c>
@@ -30170,7 +30955,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="173" spans="1:15" hidden="1">
+    <row r="173" spans="1:15">
       <c r="A173" s="34" t="s">
         <v>457</v>
       </c>
@@ -30214,7 +30999,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="174" spans="1:15" hidden="1">
+    <row r="174" spans="1:15">
       <c r="A174" s="34" t="s">
         <v>457</v>
       </c>
@@ -30258,7 +31043,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="175" spans="1:15" hidden="1">
+    <row r="175" spans="1:15">
       <c r="A175" s="34" t="s">
         <v>457</v>
       </c>
@@ -30302,7 +31087,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="176" spans="1:15" hidden="1">
+    <row r="176" spans="1:15">
       <c r="A176" s="34" t="s">
         <v>457</v>
       </c>
@@ -30346,7 +31131,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="177" spans="1:15" hidden="1">
+    <row r="177" spans="1:15">
       <c r="A177" s="34" t="s">
         <v>457</v>
       </c>
@@ -30390,7 +31175,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="178" spans="1:15" hidden="1">
+    <row r="178" spans="1:15">
       <c r="A178" s="34" t="s">
         <v>457</v>
       </c>
@@ -30434,7 +31219,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="179" spans="1:15" hidden="1">
+    <row r="179" spans="1:15">
       <c r="A179" s="34" t="s">
         <v>457</v>
       </c>
@@ -30478,7 +31263,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="180" spans="1:15" hidden="1">
+    <row r="180" spans="1:15">
       <c r="A180" s="34" t="s">
         <v>457</v>
       </c>
@@ -30522,7 +31307,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="181" spans="1:15" hidden="1">
+    <row r="181" spans="1:15">
       <c r="A181" t="s">
         <v>954</v>
       </c>
@@ -30554,7 +31339,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="182" spans="1:15" hidden="1">
+    <row r="182" spans="1:15">
       <c r="A182" t="s">
         <v>954</v>
       </c>
@@ -30586,7 +31371,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:15" hidden="1">
+    <row r="183" spans="1:15">
       <c r="A183" t="s">
         <v>954</v>
       </c>
@@ -30618,7 +31403,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="184" spans="1:15" hidden="1">
+    <row r="184" spans="1:15">
       <c r="A184" t="s">
         <v>954</v>
       </c>
@@ -30650,7 +31435,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="185" spans="1:15" hidden="1">
+    <row r="185" spans="1:15">
       <c r="A185" t="s">
         <v>954</v>
       </c>
@@ -30682,7 +31467,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="186" spans="1:15" hidden="1">
+    <row r="186" spans="1:15">
       <c r="A186" t="s">
         <v>954</v>
       </c>
@@ -30714,7 +31499,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="187" spans="1:15" hidden="1">
+    <row r="187" spans="1:15">
       <c r="A187" t="s">
         <v>954</v>
       </c>
@@ -30746,7 +31531,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="188" spans="1:15" hidden="1">
+    <row r="188" spans="1:15">
       <c r="A188" t="s">
         <v>954</v>
       </c>
@@ -30778,7 +31563,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="189" spans="1:15" hidden="1">
+    <row r="189" spans="1:15">
       <c r="A189" t="s">
         <v>954</v>
       </c>
@@ -30810,7 +31595,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="190" spans="1:15" hidden="1">
+    <row r="190" spans="1:15">
       <c r="A190" t="s">
         <v>954</v>
       </c>
@@ -30842,7 +31627,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="191" spans="1:15" hidden="1">
+    <row r="191" spans="1:15">
       <c r="A191" t="s">
         <v>954</v>
       </c>
@@ -30874,7 +31659,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="192" spans="1:15" hidden="1">
+    <row r="192" spans="1:15">
       <c r="A192" t="s">
         <v>954</v>
       </c>
@@ -30906,7 +31691,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="193" spans="1:14" hidden="1">
+    <row r="193" spans="1:14">
       <c r="A193" t="s">
         <v>954</v>
       </c>
@@ -30938,7 +31723,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="194" spans="1:14" hidden="1">
+    <row r="194" spans="1:14">
       <c r="A194" t="s">
         <v>292</v>
       </c>
@@ -30970,7 +31755,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="195" spans="1:14" hidden="1">
+    <row r="195" spans="1:14">
       <c r="A195" t="s">
         <v>292</v>
       </c>
@@ -31002,7 +31787,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="196" spans="1:14" hidden="1">
+    <row r="196" spans="1:14">
       <c r="A196" t="s">
         <v>292</v>
       </c>
@@ -31034,7 +31819,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="197" spans="1:14" hidden="1">
+    <row r="197" spans="1:14">
       <c r="A197" t="s">
         <v>292</v>
       </c>
@@ -31066,7 +31851,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="198" spans="1:14" hidden="1">
+    <row r="198" spans="1:14">
       <c r="A198" t="s">
         <v>292</v>
       </c>
@@ -31098,7 +31883,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="199" spans="1:14" hidden="1">
+    <row r="199" spans="1:14">
       <c r="A199" t="s">
         <v>292</v>
       </c>
@@ -31130,7 +31915,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="200" spans="1:14" hidden="1">
+    <row r="200" spans="1:14">
       <c r="A200" t="s">
         <v>292</v>
       </c>
@@ -31162,7 +31947,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="201" spans="1:14" hidden="1">
+    <row r="201" spans="1:14">
       <c r="A201" t="s">
         <v>292</v>
       </c>
@@ -31194,7 +31979,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="202" spans="1:14" hidden="1">
+    <row r="202" spans="1:14">
       <c r="A202" t="s">
         <v>292</v>
       </c>
@@ -31226,7 +32011,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="203" spans="1:14" hidden="1">
+    <row r="203" spans="1:14">
       <c r="A203" t="s">
         <v>292</v>
       </c>
@@ -31258,7 +32043,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="204" spans="1:14" hidden="1">
+    <row r="204" spans="1:14">
       <c r="A204" t="s">
         <v>292</v>
       </c>
@@ -31290,7 +32075,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="205" spans="1:14" hidden="1">
+    <row r="205" spans="1:14">
       <c r="A205" t="s">
         <v>292</v>
       </c>
@@ -31322,7 +32107,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="206" spans="1:14" hidden="1">
+    <row r="206" spans="1:14">
       <c r="A206" t="s">
         <v>292</v>
       </c>
@@ -31354,7 +32139,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="207" spans="1:14" hidden="1">
+    <row r="207" spans="1:14">
       <c r="A207" t="s">
         <v>292</v>
       </c>
@@ -31386,7 +32171,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="208" spans="1:14" hidden="1">
+    <row r="208" spans="1:14">
       <c r="A208" t="s">
         <v>292</v>
       </c>
@@ -31418,7 +32203,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="209" spans="1:14" hidden="1">
+    <row r="209" spans="1:14">
       <c r="A209" t="s">
         <v>292</v>
       </c>
@@ -31450,7 +32235,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="210" spans="1:14" hidden="1">
+    <row r="210" spans="1:14">
       <c r="A210" t="s">
         <v>292</v>
       </c>
@@ -31482,7 +32267,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="211" spans="1:14" hidden="1">
+    <row r="211" spans="1:14">
       <c r="A211" t="s">
         <v>292</v>
       </c>
@@ -31514,7 +32299,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="212" spans="1:14" hidden="1">
+    <row r="212" spans="1:14">
       <c r="A212" t="s">
         <v>292</v>
       </c>
@@ -31546,7 +32331,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="213" spans="1:14" hidden="1">
+    <row r="213" spans="1:14">
       <c r="A213" t="s">
         <v>292</v>
       </c>
@@ -31578,7 +32363,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="214" spans="1:14" hidden="1">
+    <row r="214" spans="1:14">
       <c r="A214" t="s">
         <v>292</v>
       </c>
@@ -31610,7 +32395,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="215" spans="1:14" hidden="1">
+    <row r="215" spans="1:14">
       <c r="A215" t="s">
         <v>292</v>
       </c>
@@ -31642,7 +32427,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="216" spans="1:14" hidden="1">
+    <row r="216" spans="1:14">
       <c r="A216" t="s">
         <v>292</v>
       </c>
@@ -31678,7 +32463,9 @@
   <autoFilter ref="A1:O216" xr:uid="{8792D24E-8DDD-4A8F-9671-F6A84E4E9306}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Au"/>
+        <filter val="Cu"/>
+        <filter val="Cu-Ni"/>
+        <filter val="Ni"/>
       </filters>
     </filterColumn>
   </autoFilter>
